--- a/public/TrackTrace_Project_Template.xlsx
+++ b/public/TrackTrace_Project_Template.xlsx
@@ -1,101 +1,96 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{05118859-EF0C-44C3-AD56-D016C18C85C0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{AFCA427A-CC3F-478E-911F-7CB791831DDE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
-  <si>
-    <t xml:space="preserve">Material Details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Width</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thickness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unique Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unique Code 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESR</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+  <si>
+    <t>articleCode</t>
+  </si>
+  <si>
+    <t>groupName</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>l1</t>
+  </si>
+  <si>
+    <t>l2</t>
+  </si>
+  <si>
+    <t>l3</t>
+  </si>
+  <si>
+    <t>qty</t>
+  </si>
+  <si>
+    <t>el1</t>
+  </si>
+  <si>
+    <t>el2</t>
+  </si>
+  <si>
+    <t>sl1</t>
+  </si>
+  <si>
+    <t>sl2</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Running Total</t>
+  </si>
+  <si>
+    <t>Count</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -107,7 +102,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -115,156 +110,224 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -272,24 +335,33 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -302,7 +374,13 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -312,13 +390,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
+                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -326,6 +406,7 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
+                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -333,40 +414,41 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0535EDB4-2F0F-4C75-8C16-5FE87D0C3720}">
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="25.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="33.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="38.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="13.22"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -400,23 +482,48 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J5" s="4"/>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/TrackTrace_Project_Template.xlsx
+++ b/public/TrackTrace_Project_Template.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -22,13 +22,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
-    <t xml:space="preserve">Material Details</t>
-  </si>
-  <si>
     <t xml:space="preserve">Item Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Description</t>
+    <t xml:space="preserve">Article Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Name</t>
   </si>
   <si>
     <t xml:space="preserve">Length</t>
@@ -44,9 +47,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unique Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unique Code 2</t>
   </si>
   <si>
     <t xml:space="preserve">ELF</t>
@@ -66,7 +66,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,6 +96,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -140,24 +147,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -181,37 +200,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -351,64 +370,67 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="25.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="33.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="38.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="13.22"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.23"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="5" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="4.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="4.32"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C2" s="0"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J5" s="4"/>
+      <c r="J5" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/public/TrackTrace_Project_Template.xlsx
+++ b/public/TrackTrace_Project_Template.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -10,17 +10,17 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve">Item Name</t>
   </si>
@@ -49,68 +49,101 @@
     <t xml:space="preserve">Unique Code</t>
   </si>
   <si>
-    <t xml:space="preserve">ELF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESR</t>
+    <t xml:space="preserve">EL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="0%"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F172A"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -122,7 +155,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -146,54 +179,173 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="2" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="12">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="20"/>
+    <cellStyle name="Comma [0]" xfId="21"/>
+    <cellStyle name="Currency" xfId="22"/>
+    <cellStyle name="Currency [0]" xfId="23"/>
+    <cellStyle name="Normal" xfId="24"/>
+    <cellStyle name="Percent" xfId="25"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0F172A"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF0F172A"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackTraceSampleTable" displayName="TrackTraceSampleTable" ref="A1:M1" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <tableColumns count="13">
+    <tableColumn id="1" name="Item Name"/>
+    <tableColumn id="2" name="Article Code"/>
+    <tableColumn id="3" name="Category Name"/>
+    <tableColumn id="4" name="Group Name"/>
+    <tableColumn id="5" name="Length"/>
+    <tableColumn id="6" name="Width"/>
+    <tableColumn id="7" name="Thickness"/>
+    <tableColumn id="8" name="Qty"/>
+    <tableColumn id="9" name="Unique Code"/>
+    <tableColumn id="10" name="EL1"/>
+    <tableColumn id="11" name="EL2"/>
+    <tableColumn id="12" name="SL1"/>
+    <tableColumn id="13" name="SL2"/>
+  </tableColumns>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -235,14 +387,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -250,67 +402,22 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -369,19 +476,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="5" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="4.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="4.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="6" customFormat="true" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -416,29 +522,22 @@
         <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C2" s="0"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J5" s="7"/>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/public/TrackTrace_Project_Template.xlsx
+++ b/public/TrackTrace_Project_Template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">Item Name</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve">SL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight</t>
   </si>
 </sst>
 </file>
@@ -476,7 +479,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
@@ -526,6 +529,9 @@
       </c>
       <c r="M1" s="4" t="s">
         <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/public/TrackTrace_Project_Template.xlsx
+++ b/public/TrackTrace_Project_Template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">Item Name</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t xml:space="preserve">Weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom Packing Group</t>
   </si>
 </sst>
 </file>
@@ -75,7 +78,7 @@
     <numFmt numFmtId="167" formatCode="0%"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -123,14 +126,6 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -211,6 +206,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -225,10 +224,6 @@
     </xf>
     <xf numFmtId="168" fontId="6" fillId="2" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -479,59 +474,65 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="5" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.62"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="5" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="8.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="10.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="12.73"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="true" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
